--- a/dataset_invalid_4_stage_missing_link/01_harvest.xlsx
+++ b/dataset_invalid_4_stage_missing_link/01_harvest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="form_event" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dictionary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="form_event" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="dictionary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y6"/>
+  <dimension ref="A1:AA6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -678,6 +678,16 @@
           <t>product_category</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>geo_lat</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>geo_lon</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -743,13 +753,11 @@
           <t>Cacao fresco</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
           <t>LOTB-HARV-001</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
       <c r="Q6" s="6" t="n">
         <v>500</v>
       </c>
@@ -773,13 +781,16 @@
           <t>DOCB-H-001</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
           <t>raw_material</t>
         </is>
+      </c>
+      <c r="Z6" t="n">
+        <v>-1.1101</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-79.4772</v>
       </c>
     </row>
   </sheetData>
